--- a/dome_site/도매_매입금.xlsx
+++ b/dome_site/도매_매입금.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,6 +446,36 @@
       </c>
       <c r="C2" t="n">
         <v>892830</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>26년06월</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>오너클랜</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>489650</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>26년04월</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>오너클랜</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1140790</v>
       </c>
     </row>
   </sheetData>

--- a/dome_site/도매_매입금.xlsx
+++ b/dome_site/도매_매입금.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,6 +478,66 @@
         <v>1140790</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>26년05월</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>젠트</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>230240</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>26년04월</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>젠트</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>289060</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>25년08월</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>오너클랜</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>335550</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>25년08월</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>젠트</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>119880</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
